--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136457569</v>
       </c>
       <c r="B3" t="n">
-        <v>92513</v>
+        <v>92516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136457569</v>
       </c>
       <c r="B3" t="n">
-        <v>92516</v>
+        <v>92517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136457569</v>
       </c>
       <c r="B3" t="n">
-        <v>92517</v>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136154324</v>
       </c>
       <c r="B4" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136457569</v>
       </c>
       <c r="B3" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136457569</v>
       </c>
       <c r="B3" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136457569</v>
       </c>
       <c r="B3" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136457569</v>
       </c>
       <c r="B3" t="n">
-        <v>92528</v>
+        <v>92529</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136457569</v>
       </c>
       <c r="B3" t="n">
-        <v>92529</v>
+        <v>92535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
